--- a/com.sevenrmartsupermarket/src/main/resources/TestData/TestData.xlsx
+++ b/com.sevenrmartsupermarket/src/main/resources/TestData/TestData.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\git\Selenium-Project\com.sevenrmartsupermarket\src\main\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF195BD-2444-4863-A1AF-A39B517BC2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF38B6CF-222E-4C51-9364-3E3498068136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DC312D3B-7033-405A-A9E8-A7886B3E794F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DC312D3B-7033-405A-A9E8-A7886B3E794F}"/>
   </bookViews>
   <sheets>
     <sheet name="AdminUser" sheetId="1" r:id="rId1"/>
+    <sheet name="ContactDetails" sheetId="2" r:id="rId2"/>
+    <sheet name="AddNews" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Username</t>
   </si>
@@ -43,16 +45,57 @@
   </si>
   <si>
     <t>anu123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone </t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Adress</t>
+  </si>
+  <si>
+    <t>Delivery Time</t>
+  </si>
+  <si>
+    <t>Delivery Charge Limit</t>
+  </si>
+  <si>
+    <t>duncan.kuhic@yahoo.com</t>
+  </si>
+  <si>
+    <t>347 Stephania Crossroad, Fenntfurt, SC 74959</t>
+  </si>
+  <si>
+    <t>075-245-9290</t>
+  </si>
+  <si>
+    <t>product added</t>
+  </si>
+  <si>
+    <t>product not found</t>
+  </si>
+  <si>
+    <t>Rainy day</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -75,13 +118,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -424,4 +470,76 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC14E12B-5B71-47F4-8B9D-EF9457E0BFB8}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{F15D5CAE-B601-4D87-99B9-6362C9309620}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B54426-5CCB-47A6-BA07-274675CBDDCB}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/com.sevenrmartsupermarket/src/main/resources/TestData/TestData.xlsx
+++ b/com.sevenrmartsupermarket/src/main/resources/TestData/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\git\Selenium-Project\com.sevenrmartsupermarket\src\main\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF38B6CF-222E-4C51-9364-3E3498068136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A234CCD5-C149-488E-8AE6-E860791502A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DC312D3B-7033-405A-A9E8-A7886B3E794F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{DC312D3B-7033-405A-A9E8-A7886B3E794F}"/>
   </bookViews>
   <sheets>
     <sheet name="AdminUser" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Username</t>
   </si>
@@ -45,21 +45,6 @@
   </si>
   <si>
     <t>anu123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone </t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Adress</t>
-  </si>
-  <si>
-    <t>Delivery Time</t>
-  </si>
-  <si>
-    <t>Delivery Charge Limit</t>
   </si>
   <si>
     <t>duncan.kuhic@yahoo.com</t>
@@ -474,46 +459,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC14E12B-5B71-47F4-8B9D-EF9457E0BFB8}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
+      <c r="D1">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="E1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{F15D5CAE-B601-4D87-99B9-6362C9309620}"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{F15D5CAE-B601-4D87-99B9-6362C9309620}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -526,17 +494,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
